--- a/data/trans_camb/IP1018-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,46</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,22</t>
+          <t>0,48; 5,42</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,0</t>
+          <t>-3,75; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-3,75; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-1,91; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,0</t>
+          <t>-2,1; 0,0</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,0</t>
+          <t>-3,15; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-3,18; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,0</t>
+          <t>-3,62; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,0</t>
+          <t>-3,15; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,17; -0,26</t>
+          <t>-2,24; -0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,16; -0,26</t>
+          <t>-2,41; -0,26</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,0</t>
+          <t>-2,39; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,0</t>
+          <t>-2,07; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1738,17 +1738,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,0</t>
+          <t>-1,35; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,35</t>
+          <t>-0,64; 0,36</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,0</t>
+          <t>-0,65; 0,0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,43</t>
+          <t>-0,35; 0,43</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; -0,07</t>
+          <t>-0,75; -0,07</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,44</t>
+          <t>-0,45; 0,46</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,54; -0,09</t>
+          <t>-0,53; -0,09</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,28</t>
+          <t>-0,28; 0,32</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-82,47; 328,82</t>
+          <t>-82,21; 395,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Provincia-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,3</t>
+          <t>0,0; 8,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,42</t>
+          <t>0,48; 5,12</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,0</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,0</t>
+          <t>-3,56; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,0</t>
+          <t>-2,65; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,0</t>
+          <t>-2,25; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,0</t>
+          <t>-3,61; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,0</t>
+          <t>-3,63; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,24; -0,26</t>
+          <t>-2,18; -0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,41; -0,26</t>
+          <t>-2,4; -0,26</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,0</t>
+          <t>-2,08; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,0</t>
+          <t>-2,49; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,0</t>
+          <t>-1,02; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,36</t>
+          <t>-0,61; 0,36</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,0</t>
+          <t>-0,71; 0,0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,43</t>
+          <t>-0,4; 0,44</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; -0,07</t>
+          <t>-0,7; -0,07</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,46</t>
+          <t>-0,46; 0,45</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; -0,09</t>
+          <t>-0,53; -0,05</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,32</t>
+          <t>-0,29; 0,36</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-82,21; 395,5</t>
+          <t>-78,66; 389,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1,69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,2</t>
+          <t>0,0; 7,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,12</t>
+          <t>0,48; 5,22</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,58</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,5; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-2,17; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-2,08; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,56</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,56</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,0</t>
+          <t>-3,12; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,0</t>
+          <t>-3,58; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,0</t>
+          <t>-3,07; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,0</t>
+          <t>-2,79; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,18; -0,26</t>
+          <t>-2,17; -0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,26</t>
+          <t>-2,16; -0,26</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,34</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,41</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-0,41</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,01</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>-2,08; 0,0</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>-2,49; 0,0</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>-1,68; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,0</t>
+          <t>-0,91; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,36</t>
+          <t>-0,64; 0,35</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-0,2</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>0,06</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>-0,73; -0,07</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>-0,43; 0,44</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>-0,71; 0,0</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 0,44</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>-0,7; -0,07</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,45</t>
+          <t>-0,37; 0,43</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; -0,05</t>
+          <t>-0,54; -0,09</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,36</t>
+          <t>-0,28; 0,28</t>
         </is>
       </c>
     </row>
@@ -1922,17 +1922,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>-15,44%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>28,43%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-15,44%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-78,66; 389,53</t>
+          <t>-82,47; 328,82</t>
         </is>
       </c>
     </row>
